--- a/output/pdf_financials_xlsx/GDC.xlsx
+++ b/output/pdf_financials_xlsx/GDC.xlsx
@@ -26287,7 +26287,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -54969,7 +54969,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -57092,7 +57092,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">

--- a/output/pdf_financials_xlsx/GDC.xlsx
+++ b/output/pdf_financials_xlsx/GDC.xlsx
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.001625</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.005202</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -7192,10 +7192,10 @@
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -37590,7 +37590,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E299" s="5" t="n">
         <v>0.001625</v>
       </c>
@@ -44294,7 +44298,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E367" s="5" t="n">
         <v>0.032528</v>
       </c>

--- a/output/pdf_financials_xlsx/GDC.xlsx
+++ b/output/pdf_financials_xlsx/GDC.xlsx
@@ -1021,37 +1021,37 @@
         <v>11.135</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>39.001</v>
+        <v>24.858</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>22.509</v>
+        <v>7.821</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>26.618</v>
+        <v>10.392</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>53.229</v>
+        <v>37.338</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>20.413</v>
+        <v>5.555</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>21.42</v>
+        <v>5.966</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>31.843</v>
+        <v>15.237</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>27.158</v>
+        <v>7.117</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>46.531</v>
+        <v>21.055</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>96.524</v>
+        <v>61.98</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>101.464</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="12">
@@ -7144,34 +7144,34 @@
         <v>-0.864</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-1.187</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.223</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.274</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.242</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.875</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.607</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-1.483</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-1.584</v>
       </c>
     </row>
     <row r="112">
@@ -8556,34 +8556,34 @@
         <v>-0.864</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-1.187</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.223</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.274</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.242</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.875</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.607</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-1.483</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-1.584</v>
       </c>
     </row>
     <row r="135">
@@ -8616,34 +8616,34 @@
         <v>41.305</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-18.325</v>
+        <v>-19.512</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>42.952</v>
+        <v>42.891</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>46.908</v>
+        <v>46.685</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>14.747</v>
+        <v>14.473</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>9.537000000000001</v>
+        <v>9.295</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>2.388</v>
+        <v>1.513</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-43.756</v>
+        <v>-44.363</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-7.799</v>
+        <v>-8.462</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>27.555</v>
+        <v>26.072</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>17.601</v>
+        <v>16.017</v>
       </c>
     </row>
   </sheetData>
@@ -30746,7 +30746,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -32756,7 +32760,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -44401,7 +44409,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E368" s="5" t="n">
         <v>-5.876345</v>
       </c>
@@ -47103,7 +47115,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
